--- a/output_forecast/bao_cao_du_bao_2026.xlsx
+++ b/output_forecast/bao_cao_du_bao_2026.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Tan suat 2026 + nam tuong tu + trung binh gan han + xu the</t>
+          <t>Tần suất 2026 + năm tương tự + trung bình gần hạn + xu thế</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Co tan suat 2026</t>
+          <t>Có tần suất 2026</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Tan suat 2026 + nam tuong tu + trung binh gan han + xu the</t>
+          <t>Tần suất 2026 + năm tương tự + trung bình gần hạn + xu thế</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Co tan suat 2026</t>
+          <t>Có tần suất 2026</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Tan suat 2026 + nam tuong tu + trung binh gan han + xu the</t>
+          <t>Tần suất 2026 + năm tương tự + trung bình gần hạn + xu thế</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Co tan suat 2026</t>
+          <t>Có tần suất 2026</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -767,17 +767,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -812,17 +812,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -853,21 +853,21 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>23.65494380746377</v>
+        <v>23.65494380746379</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -902,17 +902,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -943,21 +943,21 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>122.7770006188099</v>
+        <v>122.7770006188098</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -1033,21 +1033,21 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>54.7841657099686</v>
+        <v>54.78416570996858</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>2026</v>
       </c>
       <c r="B52" t="n">
-        <v>43.29189413776638</v>
+        <v>43.29189413776637</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>21.65519713261649</v>
       </c>
       <c r="M9" t="n">
-        <v>29.00138762920892</v>
+        <v>29.00138762920903</v>
       </c>
     </row>
     <row r="10">
@@ -11607,7 +11607,7 @@
         <v>114.7253455197128</v>
       </c>
       <c r="M11" t="n">
-        <v>121.5327701349618</v>
+        <v>121.5327701349613</v>
       </c>
     </row>
     <row r="12">
@@ -11689,7 +11689,7 @@
         <v>51.49803225806437</v>
       </c>
       <c r="M13" t="n">
-        <v>52.45177946430829</v>
+        <v>52.45177946430817</v>
       </c>
     </row>
   </sheetData>
@@ -11833,12 +11833,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tan suat 2026 + nam tuong tu + trung binh gan han + xu the</t>
+          <t>Tần suất 2026 + năm tương tự + trung bình gần hạn + xu thế</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Co tan suat 2026</t>
+          <t>Có tần suất 2026</t>
         </is>
       </c>
     </row>
@@ -11895,12 +11895,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tan suat 2026 + nam tuong tu + trung binh gan han + xu the</t>
+          <t>Tần suất 2026 + năm tương tự + trung bình gần hạn + xu thế</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Co tan suat 2026</t>
+          <t>Có tần suất 2026</t>
         </is>
       </c>
     </row>
@@ -11957,12 +11957,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tan suat 2026 + nam tuong tu + trung binh gan han + xu the</t>
+          <t>Tần suất 2026 + năm tương tự + trung bình gần hạn + xu thế</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Co tan suat 2026</t>
+          <t>Có tần suất 2026</t>
         </is>
       </c>
     </row>
@@ -12017,12 +12017,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12073,12 +12073,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12129,12 +12129,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12185,12 +12185,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12237,16 +12237,16 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>23.65494380746377</v>
+        <v>23.65494380746379</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -12267,7 +12267,7 @@
         <v>21.65519713261649</v>
       </c>
       <c r="N9" t="n">
-        <v>29.00138762920892</v>
+        <v>29.00138762920903</v>
       </c>
       <c r="O9" t="n">
         <v>20.7156660692951</v>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12349,16 +12349,16 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>122.7770006188099</v>
+        <v>122.7770006188098</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nhieu nuoc</t>
+          <t>Nhiều nước</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -12379,7 +12379,7 @@
         <v>114.7253455197128</v>
       </c>
       <c r="N11" t="n">
-        <v>121.5327701349618</v>
+        <v>121.5327701349613</v>
       </c>
       <c r="O11" t="n">
         <v>94.41778031660685</v>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12409,12 +12409,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
@@ -12461,16 +12461,16 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>54.7841657099686</v>
+        <v>54.78416570996858</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trung binh</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trung binh gan han + trung binh lich su + xu the + tham chieu 2025</t>
+          <t>Trung bình gần hạn + trung bình lịch sử + xu thế + tham chiếu 2025</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -12491,7 +12491,7 @@
         <v>51.49803225806437</v>
       </c>
       <c r="N13" t="n">
-        <v>52.45177946430829</v>
+        <v>52.45177946430817</v>
       </c>
       <c r="O13" t="n">
         <v>61.21417338709674</v>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Chua co tan suat 2026, dung mo hinh bo sung</t>
+          <t>Chưa có tần suất 2026, dùng mô hình bổ sung</t>
         </is>
       </c>
     </row>
